--- a/assets/templates/commercial-renewal-template.xlsx
+++ b/assets/templates/commercial-renewal-template.xlsx
@@ -248,7 +248,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -303,124 +303,179 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFC9D3CD"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFC9D3CD"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFC9D3CD"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFC9D3CD"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFC9D3CD"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFC9D3CD"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFC9D3CD"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFC9D3CD"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
+      <left style="thin">
+        <color rgb="FFC9D3CD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9D3CD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9D3CD"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9D3CD"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9D3CD"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC9D3CD"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9D3CD"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9D3CD"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9D3CD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9D3CD"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9D3CD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9D3CD"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9D3CD"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9D3CD"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9D3CD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9D3CD"/>
+      </right>
+      <top style="double">
         <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -437,7 +492,7 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFC9D3CD"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
@@ -455,14 +510,68 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFC9D3CD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9D3CD"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9D3CD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9D3CD"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9D3CD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9D3CD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9D3CD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9D3CD"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
@@ -660,7 +769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -718,124 +827,172 @@
     <xf numFmtId="165" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -857,14 +1014,19 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>811520</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3110884" cy="850000"/>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>798336</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -895,7 +1057,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1101,7 +1263,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="12.7109375"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="60" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="1" customWidth="1"/>
     <col min="4" max="4" width="32" style="1" customWidth="1"/>
     <col min="5" max="5" width="14" style="1" customWidth="1"/>
@@ -1349,284 +1511,284 @@
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="21"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="23">
+      <c r="E12" s="22"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="24">
         <f>IF(OR(C12="",C12=0,E12=""),"",((E12-C12)/C12))</f>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="25"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="27"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="28"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
     </row>
     <row r="13" ht="21.95" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="23">
+      <c r="C13" s="30"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="34">
         <f t="shared" ref="G13" si="0">IF(OR(C13="",C13=0,E13=""),"",((E13-C13)/C13))</f>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="28"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="30"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="38"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
     </row>
     <row r="14" ht="21.95" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="23">
+      <c r="C14" s="30"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="34">
         <f>IF(OR(C14="",C14=0,E14=""),"",((E14-C14)/C14))</f>
       </c>
-      <c r="H14" s="24" t="s">
+      <c r="H14" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="28"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="30"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="37"/>
+      <c r="M14" s="37"/>
+      <c r="N14" s="38"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
     </row>
     <row r="15" ht="21.95" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="33">
+      <c r="C15" s="40"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="43">
         <f>IF(OR(C15="",C15=0,E15=""),"",((E15-C15)/C15))</f>
       </c>
-      <c r="H15" s="34" t="s">
+      <c r="H15" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="I15" s="35"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="37"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="47"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
     </row>
     <row r="16" ht="21.95" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="23">
+      <c r="C16" s="30"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="34">
         <f t="shared" ref="G16:G20" si="1">IF(OR(C16="",C16=0,E16=""),"",((E16-C16)/C16))</f>
       </c>
-      <c r="H16" s="24" t="s">
+      <c r="H16" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="35"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="37"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="46"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="47"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
     </row>
     <row r="17" ht="21.95" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="23">
+      <c r="C17" s="30"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="34">
         <f t="shared" si="1"/>
       </c>
-      <c r="H17" s="24" t="s">
+      <c r="H17" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="28"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="29"/>
-      <c r="N17" s="30"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="37"/>
+      <c r="N17" s="38"/>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="23">
+      <c r="C18" s="30"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="34">
         <f t="shared" si="1"/>
       </c>
-      <c r="H18" s="24" t="s">
+      <c r="H18" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="28"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="30"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="37"/>
+      <c r="N18" s="38"/>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
     </row>
     <row r="19" ht="21.95" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="23">
+      <c r="C19" s="49"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="52">
         <f t="shared" si="1"/>
       </c>
-      <c r="H19" s="24" t="s">
+      <c r="H19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="38"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="39"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="40"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="55"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="55"/>
+      <c r="N19" s="56"/>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
     </row>
     <row r="20" ht="21.95" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="23">
+      <c r="B20" s="48"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="52">
         <f>IF(OR(C20="",C20=0,E20=""),"",((E20-C20)/C20))</f>
       </c>
-      <c r="H20" s="24"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="40"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="55"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="55"/>
+      <c r="N20" s="56"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
     </row>
     <row r="21" ht="21.95" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="23">
+      <c r="B21" s="48"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="52">
         <f>IF(OR(C21="",C21=0,E21=""),"",((E21-C21)/C21))</f>
       </c>
-      <c r="H21" s="24"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="40"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="56"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
     </row>
     <row r="22" ht="21.95" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="23">
+      <c r="B22" s="48"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="52">
         <f>IF(OR(C22="",C22=0,E22=""),"",((E22-C22)/C22))</f>
       </c>
-      <c r="H22" s="24"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="40"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="56"/>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="42">
+      <c r="C23" s="58">
         <f>SUM(C12:C22)</f>
       </c>
-      <c r="D23" s="43"/>
-      <c r="E23" s="42">
+      <c r="D23" s="59"/>
+      <c r="E23" s="58">
         <f>SUM(E12:E22)</f>
       </c>
-      <c r="F23" s="43"/>
-      <c r="G23" s="44">
+      <c r="F23" s="59"/>
+      <c r="G23" s="60">
         <f>IF(OR(C23="",C23=0,E23=""),"",((E23-C23)/C23))</f>
       </c>
-      <c r="H23" s="45"/>
-      <c r="I23" s="42">
+      <c r="H23" s="61"/>
+      <c r="I23" s="58">
         <f>SUM(I12:I22)</f>
       </c>
-      <c r="J23" s="42">
+      <c r="J23" s="58">
         <f>SUM(J12:J22)</f>
       </c>
-      <c r="K23" s="42">
+      <c r="K23" s="58">
         <f>SUM(K12:K22)</f>
       </c>
-      <c r="L23" s="42">
+      <c r="L23" s="58">
         <f>SUM(L12:L22)</f>
       </c>
-      <c r="M23" s="42">
+      <c r="M23" s="58">
         <f>SUM(M12:M22)</f>
       </c>
-      <c r="N23" s="46">
+      <c r="N23" s="62">
         <f>SUM(N12:N22)</f>
       </c>
       <c r="O23" s="2"/>
@@ -1673,134 +1835,134 @@
       <c r="P25" s="2"/>
     </row>
     <row r="26" ht="23.1" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="47" t="s">
+      <c r="A26" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="48" t="s">
+      <c r="B26" s="63"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48" t="s">
+      <c r="E26" s="64"/>
+      <c r="F26" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="G26" s="48"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="49"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="65"/>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
     </row>
     <row r="27" ht="46" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="50"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="53"/>
+      <c r="A27" s="66"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="69"/>
+      <c r="L27" s="69"/>
+      <c r="M27" s="69"/>
+      <c r="N27" s="69"/>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
     </row>
     <row r="28" ht="46" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="54"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="54"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="53"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="53"/>
+      <c r="A28" s="70"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="69"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="69"/>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
     </row>
     <row r="29" ht="46" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="54"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="54"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="53"/>
-      <c r="J29" s="53"/>
-      <c r="K29" s="53"/>
-      <c r="L29" s="53"/>
-      <c r="M29" s="53"/>
-      <c r="N29" s="53"/>
+      <c r="A29" s="70"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="70"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="69"/>
+      <c r="J29" s="69"/>
+      <c r="K29" s="69"/>
+      <c r="L29" s="69"/>
+      <c r="M29" s="69"/>
+      <c r="N29" s="69"/>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
     </row>
     <row r="30" ht="46" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="54"/>
-      <c r="B30" s="54"/>
-      <c r="C30" s="54"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="53"/>
-      <c r="J30" s="53"/>
-      <c r="K30" s="53"/>
-      <c r="L30" s="53"/>
-      <c r="M30" s="53"/>
-      <c r="N30" s="53"/>
+      <c r="A30" s="70"/>
+      <c r="B30" s="70"/>
+      <c r="C30" s="70"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="69"/>
+      <c r="M30" s="69"/>
+      <c r="N30" s="69"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
     </row>
     <row r="31" ht="46" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="54"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="54"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="53"/>
-      <c r="K31" s="53"/>
-      <c r="L31" s="53"/>
-      <c r="M31" s="53"/>
-      <c r="N31" s="53"/>
+      <c r="A31" s="70"/>
+      <c r="B31" s="70"/>
+      <c r="C31" s="70"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="69"/>
+      <c r="K31" s="69"/>
+      <c r="L31" s="69"/>
+      <c r="M31" s="69"/>
+      <c r="N31" s="69"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
     </row>
     <row r="32" ht="46" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="59"/>
-      <c r="B32" s="59"/>
-      <c r="C32" s="59"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
+      <c r="A32" s="75"/>
+      <c r="B32" s="75"/>
+      <c r="C32" s="75"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="53"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="53"/>
-      <c r="M32" s="53"/>
-      <c r="N32" s="53"/>
+      <c r="I32" s="69"/>
+      <c r="J32" s="69"/>
+      <c r="K32" s="69"/>
+      <c r="L32" s="69"/>
+      <c r="M32" s="69"/>
+      <c r="N32" s="69"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
     </row>
